--- a/downloads/FRB_H10_2026-08-31_to_2026-09-04.xlsx
+++ b/downloads/FRB_H10_2026-08-31_to_2026-09-04.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -53,10 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,6 +517,27 @@
           <t>2026-08-31</t>
         </is>
       </c>
+      <c r="B6" s="3" t="n">
+        <v>0.7166</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.1617</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1.3862</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.0211</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -521,6 +545,27 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="B7" s="3" t="n">
+        <v>0.7161</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.1593</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1.3527</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.5905</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1.3902</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>4.037</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -528,6 +573,27 @@
           <t>2026-09-02</t>
         </is>
       </c>
+      <c r="B8" s="3" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1.1592</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1.3503</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>4.043</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,12 +601,54 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="B9" s="3" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1.1623</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1.3536</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1.3782</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>4.0404</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.7209</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1.1618</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1.3521</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1.3834</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>4.0425</v>
       </c>
     </row>
     <row r="13">
